--- a/test-artifacts/media-reports/validated-media.xlsx
+++ b/test-artifacts/media-reports/validated-media.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,66 +402,66 @@
   <dimension ref="A1:G3"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="1" t="str">
         <v>browserId</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="1" t="str">
         <v>originalUrl</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" s="1" t="str">
         <v>finalUrl</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" s="1" t="str">
         <v>status</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" s="1" t="str">
         <v>mediaCount</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" s="1" t="str">
         <v>brokenCount</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" s="1" t="str">
         <v>error</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2" s="1" t="str">
         <v>B1-W1</v>
       </c>
-      <c r="B2" t="str">
-        <v>https://dev-suny-geneseo.pantheonsite.io/academics/</v>
-      </c>
-      <c r="C2" t="str">
-        <v>https://dev-suny-geneseo.pantheonsite.io/academics/</v>
-      </c>
-      <c r="D2" t="str">
+      <c r="B2" s="1" t="str">
+        <v>https://www.geneseo.edu/about/</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="D2" s="1" t="str">
         <v>ok</v>
       </c>
-      <c r="E2">
-        <v>7</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="E2" s="1">
+        <v>39</v>
+      </c>
+      <c r="F2" s="1">
+        <v>30</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="A3" s="1" t="str">
         <v>B1-W1</v>
       </c>
-      <c r="B3" t="str">
-        <v>https://dev-suny-geneseo.pantheonsite.io/admissions/</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://dev-suny-geneseo.pantheonsite.io/admissions/</v>
-      </c>
-      <c r="D3" t="str">
+      <c r="B3" s="1" t="str">
+        <v>https://www.geneseo.edu/apply/</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply?utm_source=postcard&amp;utm_medium=print&amp;utm_campaign=apply_early_action_0823</v>
+      </c>
+      <c r="D3" s="1" t="str">
         <v>ok</v>
       </c>
-      <c r="E3">
-        <v>25</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
+      <c r="E3" s="1">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
